--- a/artfynd/A 33791-2021 artfynd.xlsx
+++ b/artfynd/A 33791-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33791-2021 artfynd.xlsx
+++ b/artfynd/A 33791-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,128 +800,6 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>116995592</v>
-      </c>
-      <c r="B3" t="n">
-        <v>56239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100070</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sandödla</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lacerta agilis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Bakom drag 112, Drag, Sm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>585063</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6294090</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ryssby</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Niklas Nilsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Niklas Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33791-2021 artfynd.xlsx
+++ b/artfynd/A 33791-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>101578285</v>
       </c>
       <c r="B2" t="n">
-        <v>55599</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585063.0638239458</v>
+        <v>585063</v>
       </c>
       <c r="R2" t="n">
-        <v>6294089.298214943</v>
+        <v>6294090</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
